--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6494,0.1338,0.1242,0.0755</t>
-  </si>
-  <si>
-    <t>0.0262,0.0008,0.0014,0.9890</t>
-  </si>
-  <si>
-    <t>0.5893,0.0869,0.0028,0.2358</t>
-  </si>
-  <si>
-    <t>0.0502,0.0102,0.0158,0.9684</t>
-  </si>
-  <si>
-    <t>0.9955,0.0030,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0007,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9868,0.0090,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.9940,0.0008,0.0010,0.0017</t>
-  </si>
-  <si>
-    <t>0.9898,0.0061,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9816,0.0272,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9895,0.0031,0.0027,0.0013</t>
-  </si>
-  <si>
-    <t>0.9935,0.0037,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.6842,0.0358,0.1631,0.0689</t>
-  </si>
-  <si>
-    <t>0.1287,0.0826,0.7959,0.0020</t>
-  </si>
-  <si>
-    <t>0.2397,0.0089,0.8883,0.0015</t>
-  </si>
-  <si>
-    <t>0.2697,0.0391,0.7979,0.0030</t>
-  </si>
-  <si>
-    <t>0.6663,0.0753,0.2783,0.0167</t>
-  </si>
-  <si>
-    <t>0.0019,0.9941,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9966,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.1277,0.8961,0.0058,0.0037</t>
-  </si>
-  <si>
-    <t>0.0063,0.9878,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9963,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.1827,0.0096,0.8070,0.0391</t>
-  </si>
-  <si>
-    <t>0.2102,0.0804,0.7018,0.0359</t>
-  </si>
-  <si>
-    <t>0.0098,0.0184,0.9251,0.1277</t>
-  </si>
-  <si>
-    <t>0.0833,0.0134,0.9041,0.0242</t>
-  </si>
-  <si>
-    <t>0.2141,0.0101,0.8790,0.0046</t>
-  </si>
-  <si>
-    <t>0.2017,0.0355,0.7850,0.0466</t>
-  </si>
-  <si>
-    <t>0.0238,0.0038,0.9720,0.0086</t>
-  </si>
-  <si>
-    <t>0.5886,0.5750,0.0047,0.0022</t>
-  </si>
-  <si>
-    <t>0.5211,0.3852,0.1634,0.0079</t>
-  </si>
-  <si>
-    <t>0.0012,0.0186,0.9931,0.0045</t>
-  </si>
-  <si>
-    <t>0.0182,0.2274,0.8646,0.0009</t>
-  </si>
-  <si>
-    <t>0.8200,0.0830,0.0915,0.0181</t>
-  </si>
-  <si>
-    <t>0.1457,0.0590,0.8253,0.0132</t>
-  </si>
-  <si>
-    <t>0.7966,0.2608,0.0259,0.0042</t>
-  </si>
-  <si>
-    <t>0.0716,0.8822,0.2562,0.0125</t>
-  </si>
-  <si>
-    <t>0.0059,0.7139,0.3786,0.0543</t>
-  </si>
-  <si>
-    <t>0.0099,0.0183,0.9779,0.0023</t>
-  </si>
-  <si>
-    <t>0.0109,0.7735,0.7007,0.0028</t>
-  </si>
-  <si>
-    <t>0.0948,0.0437,0.8247,0.0445</t>
-  </si>
-  <si>
-    <t>0.0172,0.0455,0.9642,0.0009</t>
-  </si>
-  <si>
-    <t>0.0024,0.9420,0.1502,0.0147</t>
-  </si>
-  <si>
-    <t>0.0075,0.0131,0.9816,0.0073</t>
-  </si>
-  <si>
-    <t>0.7434,0.0683,0.0088,0.0736</t>
-  </si>
-  <si>
-    <t>0.0017,0.9911,0.0080,0.0053</t>
-  </si>
-  <si>
-    <t>0.0090,0.9558,0.1750,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9955,0.0207,0.0038</t>
-  </si>
-  <si>
-    <t>0.0004,0.0264,0.9862,0.0055</t>
-  </si>
-  <si>
-    <t>0.0111,0.1511,0.9660,0.0022</t>
-  </si>
-  <si>
-    <t>0.0216,0.0026,0.9829,0.0036</t>
-  </si>
-  <si>
-    <t>0.0679,0.0053,0.9627,0.0020</t>
-  </si>
-  <si>
-    <t>0.0093,0.0996,0.9646,0.0045</t>
-  </si>
-  <si>
-    <t>0.0014,0.0053,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.8779,0.1694,0.0155,0.0027</t>
-  </si>
-  <si>
-    <t>0.9693,0.0206,0.0097,0.0014</t>
-  </si>
-  <si>
-    <t>0.9875,0.0082,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.0251,0.2487,0.9216,0.0125</t>
-  </si>
-  <si>
-    <t>0.9700,0.0210,0.0057,0.0024</t>
-  </si>
-  <si>
-    <t>0.9870,0.0208,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9825,0.0150,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.0034,0.7638,0.9546,0.0005</t>
-  </si>
-  <si>
-    <t>0.0081,0.0289,0.9843,0.0018</t>
-  </si>
-  <si>
-    <t>0.0112,0.1801,0.9313,0.0129</t>
-  </si>
-  <si>
-    <t>0.0003,0.9309,0.9663,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0147,0.9920,0.0012</t>
-  </si>
-  <si>
-    <t>0.0249,0.9477,0.0625,0.0012</t>
-  </si>
-  <si>
-    <t>0.0034,0.9906,0.0122,0.0004</t>
-  </si>
-  <si>
-    <t>0.9806,0.0152,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.7118,0.2806,0.0472,0.0113</t>
-  </si>
-  <si>
-    <t>0.0083,0.0319,0.9445,0.0893</t>
-  </si>
-  <si>
-    <t>0.0004,0.9570,0.9288,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9302,0.9383,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9958,0.0627,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.9644,0.3869,0.0014</t>
-  </si>
-  <si>
-    <t>0.0112,0.0043,0.0116,0.9863</t>
-  </si>
-  <si>
-    <t>0.0137,0.0053,0.0027,0.9914</t>
-  </si>
-  <si>
-    <t>0.0055,0.0060,0.0004,0.9965</t>
-  </si>
-  <si>
-    <t>0.0635,0.0367,0.0047,0.9605</t>
-  </si>
-  <si>
-    <t>0.0373,0.0181,0.0038,0.9786</t>
-  </si>
-  <si>
-    <t>0.0065,0.0101,0.0065,0.9919</t>
-  </si>
-  <si>
-    <t>0.0017,0.9376,0.8463,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.8598,0.9692,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9384,0.6079,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.9040,0.8709,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.8509,0.9919,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.8707,0.6840,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0100,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9909,0.0141,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9857,0.0102,0.0029,0.0009</t>
-  </si>
-  <si>
-    <t>0.9924,0.0024,0.0006,0.0017</t>
-  </si>
-  <si>
-    <t>0.9775,0.0481,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9883,0.0120,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9908,0.0108,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0076,0.0029,0.0011</t>
-  </si>
-  <si>
-    <t>0.9964,0.0013,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9942,0.0040,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0028,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9883,0.0075,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9980,0.0008,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0004,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9896,0.0041,0.0008,0.0022</t>
-  </si>
-  <si>
-    <t>0.0029,0.0036,0.9889,0.0257</t>
-  </si>
-  <si>
-    <t>0.0300,0.0089,0.9647,0.0017</t>
-  </si>
-  <si>
-    <t>0.1959,0.0062,0.0803,0.7591</t>
-  </si>
-  <si>
-    <t>0.0114,0.0056,0.9835,0.0022</t>
-  </si>
-  <si>
-    <t>0.0166,0.9715,0.0014,0.0028</t>
-  </si>
-  <si>
-    <t>0.0016,0.9947,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0177,0.9773,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.0561,0.9473,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.0117,0.9790,0.0116,0.0005</t>
-  </si>
-  <si>
-    <t>0.0092,0.9773,0.0027,0.0044</t>
-  </si>
-  <si>
-    <t>0.4053,0.7352,0.0047,0.0007</t>
-  </si>
-  <si>
-    <t>0.6738,0.1173,0.2314,0.0160</t>
-  </si>
-  <si>
-    <t>0.4441,0.0215,0.6241,0.0164</t>
-  </si>
-  <si>
-    <t>0.3264,0.2095,0.0543,0.3559</t>
-  </si>
-  <si>
-    <t>0.4197,0.0565,0.6273,0.0263</t>
-  </si>
-  <si>
-    <t>0.1003,0.0533,0.0369,0.9087</t>
-  </si>
-  <si>
-    <t>0.0001,0.9977,0.0061,0.0027</t>
-  </si>
-  <si>
-    <t>0.0022,0.9892,0.0439,0.0008</t>
-  </si>
-  <si>
-    <t>0.0114,0.9212,0.0109,0.1678</t>
-  </si>
-  <si>
-    <t>0.0002,0.9921,0.3061,0.0006</t>
-  </si>
-  <si>
-    <t>0.0130,0.9765,0.1186,0.0003</t>
-  </si>
-  <si>
-    <t>0.5970,0.5231,0.0214,0.0017</t>
-  </si>
-  <si>
-    <t>0.4708,0.6642,0.0186,0.0014</t>
-  </si>
-  <si>
-    <t>0.9840,0.0075,0.0006,0.0026</t>
-  </si>
-  <si>
-    <t>0.9837,0.0016,0.0004,0.0109</t>
-  </si>
-  <si>
-    <t>0.9903,0.0015,0.0003,0.0047</t>
-  </si>
-  <si>
-    <t>0.9863,0.0080,0.0065,0.0004</t>
-  </si>
-  <si>
-    <t>0.9931,0.0019,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9823,0.0134,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.9810,0.0030,0.0006,0.0099</t>
-  </si>
-  <si>
-    <t>0.9913,0.0039,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.0095,0.2755,0.9569,0.0011</t>
-  </si>
-  <si>
-    <t>0.0132,0.7349,0.7160,0.0026</t>
-  </si>
-  <si>
-    <t>0.0035,0.5363,0.9373,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.0977,0.9861,0.0005</t>
-  </si>
-  <si>
-    <t>0.7723,0.1440,0.0110,0.0250</t>
-  </si>
-  <si>
-    <t>0.7212,0.0405,0.1808,0.0414</t>
-  </si>
-  <si>
-    <t>0.4113,0.0069,0.6516,0.0450</t>
-  </si>
-  <si>
-    <t>0.3351,0.4929,0.2259,0.0128</t>
-  </si>
-  <si>
-    <t>0.0515,0.0044,0.0680,0.9193</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.0002,0.9996</t>
-  </si>
-  <si>
-    <t>0.0052,0.0035,0.0007,0.9966</t>
-  </si>
-  <si>
-    <t>0.0112,0.0006,0.0007,0.9955</t>
-  </si>
-  <si>
-    <t>0.0015,0.8010,0.9277,0.0005</t>
-  </si>
-  <si>
-    <t>0.9851,0.0042,0.0007,0.0034</t>
-  </si>
-  <si>
-    <t>0.3731,0.7257,0.0074,0.0066</t>
-  </si>
-  <si>
-    <t>0.9493,0.0321,0.0007,0.0103</t>
-  </si>
-  <si>
-    <t>0.6992,0.3808,0.0235,0.0020</t>
-  </si>
-  <si>
-    <t>0.9568,0.0152,0.0239,0.0025</t>
-  </si>
-  <si>
-    <t>0.7439,0.0133,0.1555,0.0631</t>
-  </si>
-  <si>
-    <t>0.9633,0.0116,0.0222,0.0034</t>
-  </si>
-  <si>
-    <t>0.0001,0.0078,0.9935,0.0131</t>
-  </si>
-  <si>
-    <t>0.8293,0.0029,0.0650,0.0443</t>
-  </si>
-  <si>
-    <t>0.9472,0.0085,0.0073,0.0167</t>
-  </si>
-  <si>
-    <t>0.6317,0.3719,0.0290,0.0369</t>
-  </si>
-  <si>
-    <t>0.8342,0.0213,0.0409,0.0614</t>
-  </si>
-  <si>
-    <t>0.9367,0.1043,0.0047,0.0005</t>
-  </si>
-  <si>
-    <t>0.3556,0.5410,0.0192,0.0595</t>
-  </si>
-  <si>
-    <t>0.9215,0.1062,0.0036,0.0015</t>
-  </si>
-  <si>
-    <t>0.9269,0.0533,0.0226,0.0012</t>
-  </si>
-  <si>
-    <t>0.9843,0.0044,0.0012,0.0046</t>
-  </si>
-  <si>
-    <t>0.9892,0.0052,0.0008,0.0021</t>
-  </si>
-  <si>
-    <t>0.9921,0.0014,0.0005,0.0029</t>
-  </si>
-  <si>
-    <t>0.9889,0.0046,0.0014,0.0015</t>
-  </si>
-  <si>
-    <t>0.9742,0.0119,0.0044,0.0052</t>
-  </si>
-  <si>
-    <t>0.9908,0.0033,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9938,0.0012,0.0005,0.0019</t>
-  </si>
-  <si>
-    <t>0.9920,0.0028,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.8711,0.2233,0.0033,0.0028</t>
-  </si>
-  <si>
-    <t>0.2684,0.7680,0.0082,0.0096</t>
-  </si>
-  <si>
-    <t>0.6883,0.4189,0.0051,0.0039</t>
-  </si>
-  <si>
-    <t>0.1910,0.7632,0.1500,0.0030</t>
-  </si>
-  <si>
-    <t>0.9821,0.0224,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.8597,0.0138,0.1592,0.0119</t>
-  </si>
-  <si>
-    <t>0.9816,0.0271,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.8645,0.1832,0.0189,0.0012</t>
-  </si>
-  <si>
-    <t>0.0039,0.0116,0.9958,0.0003</t>
-  </si>
-  <si>
-    <t>0.9617,0.0248,0.0146,0.0012</t>
-  </si>
-  <si>
-    <t>0.0008,0.0097,0.9958,0.0017</t>
-  </si>
-  <si>
-    <t>0.0178,0.1461,0.9373,0.0014</t>
-  </si>
-  <si>
-    <t>0.0410,0.0027,0.9788,0.0021</t>
-  </si>
-  <si>
-    <t>0.0067,0.1630,0.9743,0.0023</t>
-  </si>
-  <si>
-    <t>0.0125,0.0199,0.9756,0.0052</t>
-  </si>
-  <si>
-    <t>0.0179,0.0097,0.9821,0.0025</t>
-  </si>
-  <si>
-    <t>0.0215,0.0386,0.9738,0.0010</t>
-  </si>
-  <si>
-    <t>0.2435,0.0896,0.7041,0.0145</t>
-  </si>
-  <si>
-    <t>0.2585,0.0388,0.7991,0.0075</t>
-  </si>
-  <si>
-    <t>0.4500,0.2936,0.3309,0.0065</t>
-  </si>
-  <si>
-    <t>0.2768,0.1251,0.5995,0.0085</t>
-  </si>
-  <si>
-    <t>0.1146,0.0623,0.8518,0.0007</t>
-  </si>
-  <si>
-    <t>0.4851,0.0271,0.6509,0.0090</t>
-  </si>
-  <si>
-    <t>0.4676,0.0293,0.5493,0.0245</t>
-  </si>
-  <si>
-    <t>0.1810,0.2223,0.6651,0.0072</t>
-  </si>
-  <si>
-    <t>0.5015,0.6639,0.0093,0.0014</t>
-  </si>
-  <si>
-    <t>0.3336,0.7989,0.0052,0.0005</t>
-  </si>
-  <si>
-    <t>0.7836,0.3004,0.0006,0.0026</t>
-  </si>
-  <si>
-    <t>0.9742,0.0426,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.7341,0.3585,0.0163,0.0008</t>
-  </si>
-  <si>
-    <t>0.6121,0.0967,0.2693,0.0469</t>
-  </si>
-  <si>
-    <t>0.6205,0.0220,0.4806,0.0079</t>
-  </si>
-  <si>
-    <t>0.5769,0.0178,0.0814,0.2690</t>
-  </si>
-  <si>
-    <t>0.5976,0.0013,0.2386,0.0562</t>
-  </si>
-  <si>
-    <t>0.6438,0.0577,0.3001,0.0306</t>
-  </si>
-  <si>
-    <t>0.0040,0.0082,0.9772,0.0593</t>
-  </si>
-  <si>
-    <t>0.1278,0.0647,0.7682,0.0697</t>
-  </si>
-  <si>
-    <t>0.0232,0.0936,0.9266,0.0016</t>
-  </si>
-  <si>
-    <t>0.1541,0.0968,0.7407,0.0040</t>
-  </si>
-  <si>
-    <t>0.0172,0.4923,0.7505,0.0006</t>
-  </si>
-  <si>
-    <t>0.9746,0.0267,0.0041,0.0011</t>
-  </si>
-  <si>
-    <t>0.9854,0.0137,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.9505,0.0706,0.0059,0.0009</t>
-  </si>
-  <si>
-    <t>0.9812,0.0054,0.0026,0.0042</t>
-  </si>
-  <si>
-    <t>0.9877,0.0055,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9947,0.0031,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9963,0.0015,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9745,0.0435,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.0612,0.0091,0.9739,0.0006</t>
-  </si>
-  <si>
-    <t>0.3300,0.0352,0.7792,0.0142</t>
-  </si>
-  <si>
-    <t>0.6191,0.0184,0.3479,0.0274</t>
-  </si>
-  <si>
-    <t>0.0056,0.0322,0.9850,0.0008</t>
-  </si>
-  <si>
-    <t>0.0020,0.0697,0.9811,0.0059</t>
-  </si>
-  <si>
-    <t>0.0166,0.0429,0.9601,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0025,0.9978,0.0012</t>
-  </si>
-  <si>
-    <t>0.1069,0.0384,0.8777,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0047,0.9975,0.0011</t>
-  </si>
-  <si>
-    <t>0.0049,0.1004,0.9685,0.0018</t>
-  </si>
-  <si>
-    <t>0.0799,0.0159,0.9297,0.0073</t>
-  </si>
-  <si>
-    <t>0.7279,0.0129,0.2958,0.0086</t>
-  </si>
-  <si>
-    <t>0.5076,0.0213,0.6345,0.0050</t>
-  </si>
-  <si>
-    <t>0.5461,0.0214,0.3409,0.1098</t>
-  </si>
-  <si>
-    <t>0.9892,0.0117,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9763,0.0156,0.0055,0.0018</t>
-  </si>
-  <si>
-    <t>0.9874,0.0112,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9909,0.0045,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9828,0.0165,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.9832,0.0153,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9900,0.0128,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9905,0.0035,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.0317,0.1058,0.9251,0.0017</t>
-  </si>
-  <si>
-    <t>0.0095,0.0741,0.9746,0.0011</t>
-  </si>
-  <si>
-    <t>0.0024,0.0263,0.9860,0.0010</t>
-  </si>
-  <si>
-    <t>0.0701,0.0540,0.8858,0.0010</t>
-  </si>
-  <si>
-    <t>0.0466,0.0226,0.9090,0.0288</t>
-  </si>
-  <si>
-    <t>0.1850,0.0060,0.6186,0.1952</t>
-  </si>
-  <si>
-    <t>0.0607,0.1031,0.9091,0.0019</t>
-  </si>
-  <si>
-    <t>0.0092,0.0483,0.9727,0.0033</t>
-  </si>
-  <si>
-    <t>0.5389,0.0052,0.0024,0.6954</t>
-  </si>
-  <si>
-    <t>0.0220,0.0693,0.0007,0.9773</t>
-  </si>
-  <si>
-    <t>0.0330,0.0032,0.0037,0.9844</t>
-  </si>
-  <si>
-    <t>0.0018,0.0004,0.0011,0.9985</t>
-  </si>
-  <si>
-    <t>0.0027,0.0002,0.0009,0.9980</t>
-  </si>
-  <si>
-    <t>0.3358,0.0981,0.0032,0.4849</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.5735,0.0141,0.1998,0.1578</t>
+  </si>
+  <si>
+    <t>0.0419,0.0041,0.0002,0.9862</t>
+  </si>
+  <si>
+    <t>0.3948,0.0384,0.0008,0.6312</t>
+  </si>
+  <si>
+    <t>0.1429,0.0070,0.0034,0.9393</t>
+  </si>
+  <si>
+    <t>0.9962,0.0020,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9899,0.0142,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9930,0.0030,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0024,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0065,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9938,0.0032,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9979,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7281,0.0457,0.1236,0.0361</t>
+  </si>
+  <si>
+    <t>0.4867,0.0542,0.5972,0.0050</t>
+  </si>
+  <si>
+    <t>0.3100,0.0090,0.8362,0.0028</t>
+  </si>
+  <si>
+    <t>0.0308,0.0250,0.9596,0.0023</t>
+  </si>
+  <si>
+    <t>0.8247,0.0416,0.0980,0.0103</t>
+  </si>
+  <si>
+    <t>0.0013,0.9951,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.0078,0.9885,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.0601,0.9413,0.0092,0.0016</t>
+  </si>
+  <si>
+    <t>0.0070,0.9835,0.0056,0.0005</t>
+  </si>
+  <si>
+    <t>0.0082,0.9868,0.0068,0.0001</t>
+  </si>
+  <si>
+    <t>0.1580,0.0167,0.0955,0.8082</t>
+  </si>
+  <si>
+    <t>0.3616,0.0190,0.3941,0.1659</t>
+  </si>
+  <si>
+    <t>0.0228,0.0233,0.9464,0.0163</t>
+  </si>
+  <si>
+    <t>0.1158,0.3837,0.3587,0.0076</t>
+  </si>
+  <si>
+    <t>0.0598,0.0033,0.9668,0.0034</t>
+  </si>
+  <si>
+    <t>0.0365,0.0079,0.7786,0.4289</t>
+  </si>
+  <si>
+    <t>0.0035,0.0019,0.9924,0.0021</t>
+  </si>
+  <si>
+    <t>0.3769,0.7462,0.0044,0.0017</t>
+  </si>
+  <si>
+    <t>0.4914,0.1587,0.4145,0.0101</t>
+  </si>
+  <si>
+    <t>0.0009,0.0169,0.9929,0.0050</t>
+  </si>
+  <si>
+    <t>0.0008,0.9084,0.5874,0.0000</t>
+  </si>
+  <si>
+    <t>0.8627,0.0681,0.0446,0.0185</t>
+  </si>
+  <si>
+    <t>0.5518,0.4351,0.0817,0.0122</t>
+  </si>
+  <si>
+    <t>0.8852,0.1149,0.0352,0.0011</t>
+  </si>
+  <si>
+    <t>0.0213,0.9202,0.4739,0.0039</t>
+  </si>
+  <si>
+    <t>0.0033,0.9162,0.4266,0.0055</t>
+  </si>
+  <si>
+    <t>0.0740,0.0280,0.8938,0.0175</t>
+  </si>
+  <si>
+    <t>0.0527,0.1984,0.7815,0.0587</t>
+  </si>
+  <si>
+    <t>0.3820,0.0165,0.5926,0.0463</t>
+  </si>
+  <si>
+    <t>0.0180,0.0331,0.9647,0.0011</t>
+  </si>
+  <si>
+    <t>0.0052,0.9698,0.0793,0.0043</t>
+  </si>
+  <si>
+    <t>0.0460,0.2540,0.8403,0.0084</t>
+  </si>
+  <si>
+    <t>0.0980,0.6964,0.0065,0.2549</t>
+  </si>
+  <si>
+    <t>0.0003,0.9944,0.0047,0.0139</t>
+  </si>
+  <si>
+    <t>0.0017,0.9883,0.0462,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.9939,0.0292,0.0016</t>
+  </si>
+  <si>
+    <t>0.0004,0.0217,0.9946,0.0018</t>
+  </si>
+  <si>
+    <t>0.0374,0.0847,0.9241,0.0009</t>
+  </si>
+  <si>
+    <t>0.0182,0.0141,0.9726,0.0031</t>
+  </si>
+  <si>
+    <t>0.1686,0.0172,0.8953,0.0030</t>
+  </si>
+  <si>
+    <t>0.0056,0.0290,0.9797,0.0044</t>
+  </si>
+  <si>
+    <t>0.0105,0.0400,0.9674,0.0030</t>
+  </si>
+  <si>
+    <t>0.9140,0.1350,0.0056,0.0012</t>
+  </si>
+  <si>
+    <t>0.9693,0.0159,0.0149,0.0016</t>
+  </si>
+  <si>
+    <t>0.9380,0.0740,0.0073,0.0022</t>
+  </si>
+  <si>
+    <t>0.0133,0.0561,0.9720,0.0037</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9945,0.0015,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9632,0.0546,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.0063,0.4175,0.9557,0.0018</t>
+  </si>
+  <si>
+    <t>0.0003,0.0543,0.9940,0.0011</t>
+  </si>
+  <si>
+    <t>0.0040,0.0500,0.9803,0.0037</t>
+  </si>
+  <si>
+    <t>0.0016,0.7234,0.9582,0.0001</t>
+  </si>
+  <si>
+    <t>0.0045,0.0158,0.9859,0.0048</t>
+  </si>
+  <si>
+    <t>0.0258,0.9552,0.0182,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.9854,0.0071,0.0003</t>
+  </si>
+  <si>
+    <t>0.9475,0.0518,0.0105,0.0011</t>
+  </si>
+  <si>
+    <t>0.8937,0.0553,0.0730,0.0025</t>
+  </si>
+  <si>
+    <t>0.0533,0.0659,0.8939,0.0328</t>
+  </si>
+  <si>
+    <t>0.0001,0.9812,0.8709,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9676,0.7497,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.9929,0.2052,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.9518,0.5254,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.0476,0.9868</t>
+  </si>
+  <si>
+    <t>0.0025,0.0008,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.0266,0.0111,0.0013,0.9861</t>
+  </si>
+  <si>
+    <t>0.0051,0.0053,0.0023,0.9952</t>
+  </si>
+  <si>
+    <t>0.0328,0.0171,0.0081,0.9791</t>
+  </si>
+  <si>
+    <t>0.0026,0.0027,0.0072,0.9949</t>
+  </si>
+  <si>
+    <t>0.0009,0.9588,0.8664,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.7681,0.9770,0.0002</t>
+  </si>
+  <si>
+    <t>0.0082,0.6126,0.8949,0.0012</t>
+  </si>
+  <si>
+    <t>0.0018,0.9033,0.8487,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9764,0.6554,0.0000</t>
+  </si>
+  <si>
+    <t>0.0076,0.6765,0.5715,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0041,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9893,0.0133,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0036,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9907,0.0017,0.0000,0.0029</t>
+  </si>
+  <si>
+    <t>0.9787,0.0197,0.0045,0.0010</t>
+  </si>
+  <si>
+    <t>0.9856,0.0097,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9932,0.0155,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9909,0.0054,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9946,0.0014,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9947,0.0026,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9872,0.0121,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9941,0.0029,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9957,0.0014,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0028,0.9947,0.0045</t>
+  </si>
+  <si>
+    <t>0.0446,0.0935,0.8586,0.0075</t>
+  </si>
+  <si>
+    <t>0.3542,0.0036,0.0644,0.5374</t>
+  </si>
+  <si>
+    <t>0.0172,0.0094,0.9668,0.0124</t>
+  </si>
+  <si>
+    <t>0.0050,0.9867,0.0020,0.0025</t>
+  </si>
+  <si>
+    <t>0.0030,0.9899,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.0613,0.9567,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0586,0.9459,0.0036,0.0017</t>
+  </si>
+  <si>
+    <t>0.0039,0.9906,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.0039,0.9905,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.4075,0.6177,0.0238,0.0006</t>
+  </si>
+  <si>
+    <t>0.7380,0.0322,0.1420,0.0369</t>
+  </si>
+  <si>
+    <t>0.1814,0.0361,0.8602,0.0028</t>
+  </si>
+  <si>
+    <t>0.6398,0.1062,0.2995,0.0160</t>
+  </si>
+  <si>
+    <t>0.4695,0.2010,0.3701,0.0464</t>
+  </si>
+  <si>
+    <t>0.0465,0.1111,0.0319,0.9396</t>
+  </si>
+  <si>
+    <t>0.0006,0.9966,0.0203,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9959,0.0087,0.0066</t>
+  </si>
+  <si>
+    <t>0.0346,0.8795,0.0061,0.1381</t>
+  </si>
+  <si>
+    <t>0.0001,0.9857,0.8423,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.9892,0.0266,0.0004</t>
+  </si>
+  <si>
+    <t>0.7169,0.0484,0.2908,0.0002</t>
+  </si>
+  <si>
+    <t>0.5912,0.3481,0.0897,0.0006</t>
+  </si>
+  <si>
+    <t>0.9863,0.0047,0.0013,0.0030</t>
+  </si>
+  <si>
+    <t>0.9925,0.0013,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.9878,0.0038,0.0011,0.0027</t>
+  </si>
+  <si>
+    <t>0.9680,0.0091,0.0224,0.0022</t>
+  </si>
+  <si>
+    <t>0.9955,0.0014,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9812,0.0160,0.0044,0.0008</t>
+  </si>
+  <si>
+    <t>0.9924,0.0018,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.9596,0.0262,0.0158,0.0011</t>
+  </si>
+  <si>
+    <t>0.0011,0.9294,0.9303,0.0002</t>
+  </si>
+  <si>
+    <t>0.0084,0.5488,0.8806,0.0011</t>
+  </si>
+  <si>
+    <t>0.0021,0.3929,0.9685,0.0004</t>
+  </si>
+  <si>
+    <t>0.0053,0.3149,0.9598,0.0004</t>
+  </si>
+  <si>
+    <t>0.2992,0.0537,0.0166,0.7330</t>
+  </si>
+  <si>
+    <t>0.2588,0.1284,0.6979,0.0235</t>
+  </si>
+  <si>
+    <t>0.3568,0.0095,0.6678,0.0876</t>
+  </si>
+  <si>
+    <t>0.3700,0.1100,0.5757,0.0394</t>
+  </si>
+  <si>
+    <t>0.0082,0.0007,0.0024,0.9945</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.0007,0.9990</t>
+  </si>
+  <si>
+    <t>0.0402,0.0030,0.0023,0.9860</t>
+  </si>
+  <si>
+    <t>0.0755,0.0036,0.0034,0.9744</t>
+  </si>
+  <si>
+    <t>0.0002,0.9173,0.8761,0.0007</t>
+  </si>
+  <si>
+    <t>0.9691,0.0133,0.0003,0.0062</t>
+  </si>
+  <si>
+    <t>0.8049,0.1939,0.0050,0.0145</t>
+  </si>
+  <si>
+    <t>0.9681,0.0106,0.0009,0.0108</t>
+  </si>
+  <si>
+    <t>0.8069,0.3488,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.9775,0.0021,0.0055,0.0055</t>
+  </si>
+  <si>
+    <t>0.7915,0.0104,0.1031,0.0572</t>
+  </si>
+  <si>
+    <t>0.9462,0.0232,0.0264,0.0067</t>
+  </si>
+  <si>
+    <t>0.0000,0.0360,0.9972,0.0012</t>
+  </si>
+  <si>
+    <t>0.9067,0.0011,0.0124,0.0534</t>
+  </si>
+  <si>
+    <t>0.9106,0.0038,0.0304,0.0238</t>
+  </si>
+  <si>
+    <t>0.6662,0.3612,0.0339,0.0027</t>
+  </si>
+  <si>
+    <t>0.9300,0.0472,0.0086,0.0050</t>
+  </si>
+  <si>
+    <t>0.9801,0.0184,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.3758,0.6755,0.0318,0.0081</t>
+  </si>
+  <si>
+    <t>0.8396,0.1933,0.0098,0.0038</t>
+  </si>
+  <si>
+    <t>0.8958,0.0556,0.0210,0.0064</t>
+  </si>
+  <si>
+    <t>0.9885,0.0053,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9904,0.0048,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9816,0.0139,0.0070,0.0005</t>
+  </si>
+  <si>
+    <t>0.9895,0.0017,0.0022,0.0025</t>
+  </si>
+  <si>
+    <t>0.9889,0.0058,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9897,0.0025,0.0039,0.0012</t>
+  </si>
+  <si>
+    <t>0.9944,0.0022,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0005,0.0001,0.0079</t>
+  </si>
+  <si>
+    <t>0.8985,0.1323,0.0190,0.0021</t>
+  </si>
+  <si>
+    <t>0.8692,0.1534,0.0261,0.0021</t>
+  </si>
+  <si>
+    <t>0.8173,0.2723,0.0130,0.0026</t>
+  </si>
+  <si>
+    <t>0.4897,0.2676,0.4016,0.0030</t>
+  </si>
+  <si>
+    <t>0.9536,0.0500,0.0088,0.0011</t>
+  </si>
+  <si>
+    <t>0.9612,0.0330,0.0051,0.0026</t>
+  </si>
+  <si>
+    <t>0.9882,0.0067,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.8460,0.1598,0.0415,0.0086</t>
+  </si>
+  <si>
+    <t>0.0017,0.0179,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.9119,0.1306,0.0097,0.0015</t>
+  </si>
+  <si>
+    <t>0.0093,0.0535,0.9748,0.0017</t>
+  </si>
+  <si>
+    <t>0.0013,0.0772,0.9918,0.0004</t>
+  </si>
+  <si>
+    <t>0.0198,0.0082,0.9809,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.3370,0.9839,0.0006</t>
+  </si>
+  <si>
+    <t>0.0414,0.0324,0.9566,0.0026</t>
+  </si>
+  <si>
+    <t>0.0071,0.0080,0.9903,0.0007</t>
+  </si>
+  <si>
+    <t>0.0075,0.0144,0.9893,0.0009</t>
+  </si>
+  <si>
+    <t>0.2307,0.0275,0.8323,0.0062</t>
+  </si>
+  <si>
+    <t>0.1616,0.0639,0.8085,0.0016</t>
+  </si>
+  <si>
+    <t>0.7544,0.0281,0.1616,0.0228</t>
+  </si>
+  <si>
+    <t>0.0662,0.0081,0.9533,0.0051</t>
+  </si>
+  <si>
+    <t>0.2261,0.2578,0.4733,0.0022</t>
+  </si>
+  <si>
+    <t>0.5320,0.0917,0.4449,0.0309</t>
+  </si>
+  <si>
+    <t>0.4103,0.0694,0.5898,0.0239</t>
+  </si>
+  <si>
+    <t>0.1182,0.6357,0.3116,0.0036</t>
+  </si>
+  <si>
+    <t>0.8326,0.2928,0.0063,0.0014</t>
+  </si>
+  <si>
+    <t>0.9464,0.1169,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.9563,0.0721,0.0036,0.0007</t>
+  </si>
+  <si>
+    <t>0.9788,0.0350,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.7155,0.4636,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.1716,0.5434,0.3240,0.0954</t>
+  </si>
+  <si>
+    <t>0.3488,0.0209,0.7840,0.0037</t>
+  </si>
+  <si>
+    <t>0.4385,0.2288,0.1125,0.3236</t>
+  </si>
+  <si>
+    <t>0.6027,0.0473,0.3735,0.0351</t>
+  </si>
+  <si>
+    <t>0.5823,0.0236,0.2656,0.0846</t>
+  </si>
+  <si>
+    <t>0.0092,0.0070,0.9721,0.0576</t>
+  </si>
+  <si>
+    <t>0.0509,0.2244,0.8127,0.0076</t>
+  </si>
+  <si>
+    <t>0.0559,0.0459,0.9140,0.0081</t>
+  </si>
+  <si>
+    <t>0.0669,0.0895,0.8625,0.0064</t>
+  </si>
+  <si>
+    <t>0.0095,0.3314,0.9156,0.0014</t>
+  </si>
+  <si>
+    <t>0.9705,0.0214,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9886,0.0061,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9932,0.0045,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9866,0.0072,0.0055,0.0011</t>
+  </si>
+  <si>
+    <t>0.9869,0.0102,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9932,0.0089,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9892,0.0105,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9921,0.0034,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.0118,0.0041,0.9899,0.0016</t>
+  </si>
+  <si>
+    <t>0.4794,0.2981,0.3657,0.0091</t>
+  </si>
+  <si>
+    <t>0.8556,0.0820,0.0201,0.0288</t>
+  </si>
+  <si>
+    <t>0.0031,0.0395,0.9878,0.0003</t>
+  </si>
+  <si>
+    <t>0.0030,0.0073,0.9850,0.0115</t>
+  </si>
+  <si>
+    <t>0.0282,0.3331,0.8145,0.0051</t>
+  </si>
+  <si>
+    <t>0.0091,0.0520,0.9728,0.0001</t>
+  </si>
+  <si>
+    <t>0.2697,0.0119,0.8279,0.0072</t>
+  </si>
+  <si>
+    <t>0.0012,0.0056,0.9945,0.0018</t>
+  </si>
+  <si>
+    <t>0.0166,0.1355,0.9441,0.0010</t>
+  </si>
+  <si>
+    <t>0.1190,0.1876,0.7393,0.0134</t>
+  </si>
+  <si>
+    <t>0.6098,0.0221,0.2460,0.0836</t>
+  </si>
+  <si>
+    <t>0.6788,0.0066,0.2167,0.0434</t>
+  </si>
+  <si>
+    <t>0.4578,0.0112,0.5178,0.0571</t>
+  </si>
+  <si>
+    <t>0.9885,0.0041,0.0010,0.0032</t>
+  </si>
+  <si>
+    <t>0.9926,0.0032,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9881,0.0080,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9606,0.0309,0.0210,0.0004</t>
+  </si>
+  <si>
+    <t>0.9814,0.0040,0.0001,0.0048</t>
+  </si>
+  <si>
+    <t>0.9943,0.0026,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9759,0.0244,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.9929,0.0024,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.0089,0.1027,0.9592,0.0010</t>
+  </si>
+  <si>
+    <t>0.0079,0.1047,0.9712,0.0008</t>
+  </si>
+  <si>
+    <t>0.0049,0.0387,0.9845,0.0019</t>
+  </si>
+  <si>
+    <t>0.1104,0.0788,0.8113,0.0172</t>
+  </si>
+  <si>
+    <t>0.0005,0.0043,0.9946,0.0042</t>
+  </si>
+  <si>
+    <t>0.2333,0.0073,0.7259,0.0562</t>
+  </si>
+  <si>
+    <t>0.0580,0.0211,0.9241,0.0171</t>
+  </si>
+  <si>
+    <t>0.0427,0.0640,0.7836,0.0848</t>
+  </si>
+  <si>
+    <t>0.4818,0.0058,0.0137,0.6519</t>
+  </si>
+  <si>
+    <t>0.0430,0.0312,0.0061,0.9711</t>
+  </si>
+  <si>
+    <t>0.0102,0.0065,0.0015,0.9938</t>
+  </si>
+  <si>
+    <t>0.0008,0.0009,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0112,0.0008,0.0005,0.9956</t>
+  </si>
+  <si>
+    <t>0.6420,0.0901,0.0040,0.1486</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1984,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2337,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2477,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3135,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3888,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3930,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4591,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4770,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4784,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4798,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5204,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
